--- a/BVSimulationFiles/57.xlsx
+++ b/BVSimulationFiles/57.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002070707070707071</v>
+        <v>0.004141414141414142</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002003106536131004</v>
+        <v>0.004006213072262008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001937712896165778</v>
+        <v>0.003875425792331556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00187445410428315</v>
+        <v>0.0037489082085663</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0018132604659939</v>
+        <v>0.0036265209319878</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001754064562062892</v>
+        <v>0.003508129124125784</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001696801174230882</v>
+        <v>0.003393602348461764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001641407213361208</v>
+        <v>0.003282814426722416</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00158782164993222</v>
+        <v>0.00317564329986444</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001535985446798854</v>
+        <v>0.003071970893597708</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001485841494149286</v>
+        <v>0.002971682988298572</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001437334546584997</v>
+        <v>0.002874669093169994</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001390411162254921</v>
+        <v>0.002780822324509842</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001345019643976642</v>
+        <v>0.002690039287953284</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001301109982279739</v>
+        <v>0.002602219964559478</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001258633800308558</v>
+        <v>0.002517267600617116</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00121754430052368</v>
+        <v>0.00243508860104736</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001177796213143393</v>
+        <v>0.002355592426286786</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00113934574626834</v>
+        <v>0.00227869149253668</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001102150537634409</v>
+        <v>0.002204301075268818</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002070707070707071</v>
+        <v>0.004141414141414142</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002003106536131004</v>
+        <v>0.004006213072262008</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001937712896165778</v>
+        <v>0.003875425792331556</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00187445410428315</v>
+        <v>0.0037489082085663</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0018132604659939</v>
+        <v>0.0036265209319878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001754064562062892</v>
+        <v>0.003508129124125784</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001696801174230882</v>
+        <v>0.003393602348461764</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001641407213361208</v>
+        <v>0.003282814426722416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00158782164993222</v>
+        <v>0.00317564329986444</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001535985446798854</v>
+        <v>0.003071970893597708</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001485841494149286</v>
+        <v>0.002971682988298572</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001437334546584997</v>
+        <v>0.002874669093169994</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001390411162254921</v>
+        <v>0.002780822324509842</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001345019643976642</v>
+        <v>0.002690039287953284</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001301109982279739</v>
+        <v>0.002602219964559478</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001258633800308558</v>
+        <v>0.002517267600617116</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00121754430052368</v>
+        <v>0.00243508860104736</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001177796213143393</v>
+        <v>0.002355592426286786</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00113934574626834</v>
+        <v>0.00227869149253668</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001102150537634409</v>
+        <v>0.002204301075268818</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/57.xlsx
+++ b/BVSimulationFiles/57.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004141414141414142</v>
+        <v>0.04141414141414142</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004006213072262008</v>
+        <v>0.04006213072262008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003875425792331556</v>
+        <v>0.03875425792331556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0037489082085663</v>
+        <v>0.037489082085663</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0036265209319878</v>
+        <v>0.036265209319878</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003508129124125784</v>
+        <v>0.03508129124125784</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003393602348461764</v>
+        <v>0.03393602348461764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003282814426722416</v>
+        <v>0.03282814426722416</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00317564329986444</v>
+        <v>0.0317564329986444</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003071970893597708</v>
+        <v>0.03071970893597708</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002971682988298572</v>
+        <v>0.02971682988298572</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002874669093169994</v>
+        <v>0.02874669093169994</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002780822324509842</v>
+        <v>0.02780822324509842</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002690039287953284</v>
+        <v>0.02690039287953284</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002602219964559478</v>
+        <v>0.02602219964559478</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002517267600617116</v>
+        <v>0.02517267600617116</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00243508860104736</v>
+        <v>0.0243508860104736</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002355592426286786</v>
+        <v>0.02355592426286786</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00227869149253668</v>
+        <v>0.0227869149253668</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002204301075268818</v>
+        <v>0.02204301075268818</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004141414141414142</v>
+        <v>0.04141414141414142</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004006213072262008</v>
+        <v>0.04006213072262008</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003875425792331556</v>
+        <v>0.03875425792331556</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0037489082085663</v>
+        <v>0.037489082085663</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0036265209319878</v>
+        <v>0.036265209319878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003508129124125784</v>
+        <v>0.03508129124125784</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003393602348461764</v>
+        <v>0.03393602348461764</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003282814426722416</v>
+        <v>0.03282814426722416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00317564329986444</v>
+        <v>0.0317564329986444</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003071970893597708</v>
+        <v>0.03071970893597708</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002971682988298572</v>
+        <v>0.02971682988298572</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002874669093169994</v>
+        <v>0.02874669093169994</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002780822324509842</v>
+        <v>0.02780822324509842</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002690039287953284</v>
+        <v>0.02690039287953284</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002602219964559478</v>
+        <v>0.02602219964559478</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002517267600617116</v>
+        <v>0.02517267600617116</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00243508860104736</v>
+        <v>0.0243508860104736</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002355592426286786</v>
+        <v>0.02355592426286786</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00227869149253668</v>
+        <v>0.0227869149253668</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002204301075268818</v>
+        <v>0.02204301075268818</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/57.xlsx
+++ b/BVSimulationFiles/57.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04141414141414142</v>
+        <v>0.3328921878771405</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04006213072262008</v>
+        <v>0.3115117027451476</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03875425792331556</v>
+        <v>0.2915044103798412</v>
       </c>
       <c r="E2" t="n">
-        <v>0.037489082085663</v>
+        <v>0.2727821154777548</v>
       </c>
       <c r="F2" t="n">
-        <v>0.036265209319878</v>
+        <v>0.255262287207113</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03508129124125784</v>
+        <v>0.2388676953988954</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03393602348461764</v>
+        <v>0.2235260701040586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03282814426722416</v>
+        <v>0.2091697830161908</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0317564329986444</v>
+        <v>0.1957355493552603</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03071970893597708</v>
+        <v>0.1831641488983138</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02971682988298572</v>
+        <v>0.1714001649273837</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02874669093169994</v>
+        <v>0.1603917399438465</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02780822324509842</v>
+        <v>0.1500903470723817</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02690039287953284</v>
+        <v>0.1404505761468439</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02602219964559478</v>
+        <v>0.1314299335350813</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02517267600617116</v>
+        <v>0.1229886548202958</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0243508860104736</v>
+        <v>0.115089529513217</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02355592426286786</v>
+        <v>0.1076977370223895</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0227869149253668</v>
+        <v>0.1007806931595088</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02204301075268818</v>
+        <v>0.09430790650317533</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04141414141414142</v>
+        <v>0.3328921878771405</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04006213072262008</v>
+        <v>0.3115117027451476</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03875425792331556</v>
+        <v>0.2915044103798412</v>
       </c>
       <c r="E3" t="n">
-        <v>0.037489082085663</v>
+        <v>0.2727821154777548</v>
       </c>
       <c r="F3" t="n">
-        <v>0.036265209319878</v>
+        <v>0.255262287207113</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03508129124125784</v>
+        <v>0.2388676953988954</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03393602348461764</v>
+        <v>0.2235260701040586</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03282814426722416</v>
+        <v>0.2091697830161908</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0317564329986444</v>
+        <v>0.1957355493552603</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03071970893597708</v>
+        <v>0.1831641488983138</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02971682988298572</v>
+        <v>0.1714001649273837</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02874669093169994</v>
+        <v>0.1603917399438465</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02780822324509842</v>
+        <v>0.1500903470723817</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02690039287953284</v>
+        <v>0.1404505761468439</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02602219964559478</v>
+        <v>0.1314299335350813</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02517267600617116</v>
+        <v>0.1229886548202958</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0243508860104736</v>
+        <v>0.115089529513217</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02355592426286786</v>
+        <v>0.1076977370223895</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0227869149253668</v>
+        <v>0.1007806931595088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02204301075268818</v>
+        <v>0.09430790650317533</v>
       </c>
     </row>
   </sheetData>
